--- a/e2e-screenshots/return-types-round-trip/downloaded-inventory-report.xlsx
+++ b/e2e-screenshots/return-types-round-trip/downloaded-inventory-report.xlsx
@@ -557,7 +557,7 @@
         <v>21</v>
       </c>
       <c r="L2">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/e2e-screenshots/return-types-round-trip/downloaded-inventory-report.xlsx
+++ b/e2e-screenshots/return-types-round-trip/downloaded-inventory-report.xlsx
@@ -557,7 +557,7 @@
         <v>21</v>
       </c>
       <c r="L2">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/e2e-screenshots/return-types-round-trip/downloaded-inventory-report.xlsx
+++ b/e2e-screenshots/return-types-round-trip/downloaded-inventory-report.xlsx
@@ -557,7 +557,7 @@
         <v>21</v>
       </c>
       <c r="L2">
-        <v>65</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/e2e-screenshots/return-types-round-trip/downloaded-inventory-report.xlsx
+++ b/e2e-screenshots/return-types-round-trip/downloaded-inventory-report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="24">
   <si>
     <t>Stock In Date</t>
   </si>
@@ -50,6 +50,9 @@
     <t>Age (days)</t>
   </si>
   <si>
+    <t>Return Date</t>
+  </si>
+  <si>
     <t>2026-06-01</t>
   </si>
   <si>
@@ -78,6 +81,9 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>2026-08-28</t>
   </si>
 </sst>
 </file>
@@ -474,17 +480,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="10" width="14" customWidth="1"/>
     <col min="11" max="11" width="30" customWidth="1"/>
-    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="12" max="13" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -521,47 +527,53 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I2">
         <v>350</v>
       </c>
       <c r="J2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L2">
         <v>88</v>
       </c>
+      <c r="M2" t="s">
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:M1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -569,17 +581,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="10" width="14" customWidth="1"/>
     <col min="11" max="11" width="30" customWidth="1"/>
-    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="12" max="13" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -616,9 +628,12 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:M1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/e2e-screenshots/return-types-round-trip/downloaded-inventory-report.xlsx
+++ b/e2e-screenshots/return-types-round-trip/downloaded-inventory-report.xlsx
@@ -83,7 +83,7 @@
     <t/>
   </si>
   <si>
-    <t>2026-08-28</t>
+    <t>2026-08-29</t>
   </si>
 </sst>
 </file>
@@ -566,7 +566,7 @@
         <v>22</v>
       </c>
       <c r="L2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M2" t="s">
         <v>23</v>

--- a/e2e-screenshots/return-types-round-trip/downloaded-inventory-report.xlsx
+++ b/e2e-screenshots/return-types-round-trip/downloaded-inventory-report.xlsx
@@ -83,7 +83,7 @@
     <t/>
   </si>
   <si>
-    <t>2026-08-29</t>
+    <t>2026-09-02</t>
   </si>
 </sst>
 </file>
@@ -566,7 +566,7 @@
         <v>22</v>
       </c>
       <c r="L2">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="M2" t="s">
         <v>23</v>

--- a/e2e-screenshots/return-types-round-trip/downloaded-inventory-report.xlsx
+++ b/e2e-screenshots/return-types-round-trip/downloaded-inventory-report.xlsx
@@ -83,7 +83,7 @@
     <t/>
   </si>
   <si>
-    <t>2026-09-02</t>
+    <t>2026-09-05</t>
   </si>
 </sst>
 </file>
@@ -566,7 +566,7 @@
         <v>22</v>
       </c>
       <c r="L2">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="M2" t="s">
         <v>23</v>

--- a/e2e-screenshots/return-types-round-trip/downloaded-inventory-report.xlsx
+++ b/e2e-screenshots/return-types-round-trip/downloaded-inventory-report.xlsx
@@ -83,7 +83,7 @@
     <t/>
   </si>
   <si>
-    <t>2026-09-05</t>
+    <t>2026-09-09</t>
   </si>
 </sst>
 </file>
@@ -566,7 +566,7 @@
         <v>22</v>
       </c>
       <c r="L2">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M2" t="s">
         <v>23</v>
